--- a/1_Solid_CAD_Model/15 kg version/ORGO_Avionics/12S_VTOL_Electronics_Comparison_ChatGPT.xlsx
+++ b/1_Solid_CAD_Model/15 kg version/ORGO_Avionics/12S_VTOL_Electronics_Comparison_ChatGPT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drones\ORGOfly-CAD-model\1_Solid_CAD_Model\15 kg version\ORGO_Avionics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE2E459A-A259-4B4A-8B1B-252AEDED42C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E6BF26-1EDB-4E1B-85D2-00FE6DF0C7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FC" sheetId="1" r:id="rId1"/>
@@ -2617,7 +2617,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\€#,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -2638,6 +2638,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -2673,10 +2679,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2710,8 +2717,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
@@ -3672,7 +3683,7 @@
       <c r="M14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="N14" s="13" t="s">
         <v>107</v>
       </c>
     </row>
@@ -5043,9 +5054,12 @@
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="N14" r:id="rId1" xr:uid="{A64E6FE7-D743-424B-89C6-63BEDBE8D046}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6743,7 +6757,7 @@
       <c r="M6" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="N6" s="13" t="s">
         <v>246</v>
       </c>
     </row>
@@ -6878,7 +6892,7 @@
       <c r="M9" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="N9" s="13" t="s">
         <v>275</v>
       </c>
     </row>
@@ -7058,7 +7072,7 @@
       <c r="M13" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="N13" s="3" t="s">
+      <c r="N13" s="13" t="s">
         <v>309</v>
       </c>
     </row>
@@ -7103,7 +7117,7 @@
       <c r="M14" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="N14" s="13" t="s">
         <v>319</v>
       </c>
     </row>
@@ -8165,9 +8179,15 @@
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="N13" r:id="rId1" xr:uid="{DAEBC427-26AB-46E1-A696-0402CC2840EB}"/>
+    <hyperlink ref="N14" r:id="rId2" xr:uid="{765DD7EA-4D25-4AAA-AC2A-528BC168819E}"/>
+    <hyperlink ref="N6" r:id="rId3" xr:uid="{47966538-B36D-4F11-B2F2-16891E862FDF}"/>
+    <hyperlink ref="N9" r:id="rId4" xr:uid="{F7E38E8B-7C8A-4AB5-B12A-7FD137BD71F6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8314,7 +8334,7 @@
       <c r="M5" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="13" t="s">
         <v>353</v>
       </c>
     </row>
@@ -9393,9 +9413,12 @@
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="N5" r:id="rId1" xr:uid="{A4362D32-992F-4DF2-B7E0-CC6242AD5132}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -10774,7 +10797,7 @@
       <c r="M6" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="N6" s="13" t="s">
         <v>495</v>
       </c>
     </row>
@@ -11767,9 +11790,12 @@
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="N6" r:id="rId1" xr:uid="{6AEF975F-2F45-4E91-984F-A00B129DF3A7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
